--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_01C_2026.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_01C_2026.xlsx
@@ -533,17 +533,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -551,13 +543,21 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="2"/>
@@ -866,68 +866,68 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="26" t="s">
+      <c r="O1" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-    </row>
-    <row r="2" spans="1:22" s="34" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
-      <c r="T2" s="32"/>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-    </row>
-    <row r="3" spans="1:22" s="34" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="32" t="s">
+      <c r="P1" s="33"/>
+      <c r="Q1" s="33"/>
+      <c r="R1" s="33"/>
+      <c r="S1" s="33"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="33"/>
+      <c r="V1" s="33"/>
+    </row>
+    <row r="2" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+    </row>
+    <row r="3" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="S3" s="32"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
     </row>
     <row r="4" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
@@ -945,199 +945,199 @@
       <c r="P4" s="20"/>
       <c r="Q4" s="20"/>
     </row>
-    <row r="5" spans="1:22" s="34" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-    </row>
-    <row r="6" spans="1:22" s="34" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
+    <row r="5" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34"/>
+    </row>
+    <row r="6" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="34"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="33"/>
-      <c r="V7" s="33"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
     </row>
     <row r="8" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="29" t="s">
+      <c r="D8" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="30"/>
+      <c r="P8" s="30"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="30"/>
+      <c r="S8" s="30"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="30"/>
+      <c r="V8" s="30"/>
     </row>
     <row r="9" spans="1:22" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="28" t="s">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="28" t="s">
+      <c r="J9" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="28" t="s">
+      <c r="K9" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="28" t="s">
+      <c r="L9" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="28" t="s">
+      <c r="N9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="28" t="s">
+      <c r="O9" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="P9" s="28" t="s">
+      <c r="P9" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="28"/>
-      <c r="R9" s="28" t="s">
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="28" t="s">
+      <c r="S9" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="28" t="s">
+      <c r="T9" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="U9" s="30" t="s">
+      <c r="U9" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="V9" s="30" t="s">
+      <c r="V9" s="28" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:22" s="14" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="24" t="s">
         <v>40</v>
       </c>
       <c r="Q10" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
@@ -1281,7 +1281,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="5"/>
       <c r="E13" s="22">
-        <f>SUM(F13:P14)+ SUM(R13+V13)</f>
+        <f>SUM(F13:V13) -Q13</f>
         <v>0</v>
       </c>
       <c r="F13" s="9"/>
@@ -1308,7 +1308,7 @@
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
       <c r="E14" s="22">
-        <f t="shared" ref="E14:E77" si="0">SUM(F14:P15)+ SUM(R14+V14)</f>
+        <f t="shared" ref="E14:E77" si="0">SUM(F14:V14) -Q14</f>
         <v>0</v>
       </c>
       <c r="F14" s="11"/>
@@ -3036,7 +3036,7 @@
       <c r="C78" s="8"/>
       <c r="D78" s="7"/>
       <c r="E78" s="22">
-        <f t="shared" ref="E78:E141" si="1">SUM(F78:P79)+ SUM(R78+V78)</f>
+        <f t="shared" ref="E78:E141" si="1">SUM(F78:V78) -Q78</f>
         <v>0</v>
       </c>
       <c r="F78" s="11"/>
@@ -4764,7 +4764,7 @@
       <c r="C142" s="8"/>
       <c r="D142" s="7"/>
       <c r="E142" s="22">
-        <f t="shared" ref="E142:E205" si="2">SUM(F142:P143)+ SUM(R142+V142)</f>
+        <f t="shared" ref="E142:E205" si="2">SUM(F142:V142) -Q142</f>
         <v>0</v>
       </c>
       <c r="F142" s="11"/>
@@ -6492,7 +6492,7 @@
       <c r="C206" s="8"/>
       <c r="D206" s="7"/>
       <c r="E206" s="22">
-        <f t="shared" ref="E206:E269" si="3">SUM(F206:P207)+ SUM(R206+V206)</f>
+        <f t="shared" ref="E206:E269" si="3">SUM(F206:V206) -Q206</f>
         <v>0</v>
       </c>
       <c r="F206" s="11"/>
@@ -8220,7 +8220,7 @@
       <c r="C270" s="17"/>
       <c r="D270" s="18"/>
       <c r="E270" s="22">
-        <f t="shared" ref="E270:E333" si="4">SUM(F270:P271)+ SUM(R270+V270)</f>
+        <f t="shared" ref="E270:E333" si="4">SUM(F270:V270) -Q270</f>
         <v>0</v>
       </c>
       <c r="F270" s="19"/>
@@ -9948,7 +9948,7 @@
       <c r="C334" s="17"/>
       <c r="D334" s="18"/>
       <c r="E334" s="22">
-        <f t="shared" ref="E334:E397" si="5">SUM(F334:P335)+ SUM(R334+V334)</f>
+        <f t="shared" ref="E334:E397" si="5">SUM(F334:V334) -Q334</f>
         <v>0</v>
       </c>
       <c r="F334" s="19"/>
@@ -11676,7 +11676,7 @@
       <c r="C398" s="17"/>
       <c r="D398" s="18"/>
       <c r="E398" s="22">
-        <f t="shared" ref="E398:E461" si="6">SUM(F398:P399)+ SUM(R398+V398)</f>
+        <f t="shared" ref="E398:E461" si="6">SUM(F398:V398) -Q398</f>
         <v>0</v>
       </c>
       <c r="F398" s="19"/>
@@ -13404,7 +13404,7 @@
       <c r="C462" s="17"/>
       <c r="D462" s="18"/>
       <c r="E462" s="22">
-        <f t="shared" ref="E462:E525" si="7">SUM(F462:P463)+ SUM(R462+V462)</f>
+        <f t="shared" ref="E462:E525" si="7">SUM(F462:V462) -Q462</f>
         <v>0</v>
       </c>
       <c r="F462" s="19"/>
@@ -15132,7 +15132,7 @@
       <c r="C526" s="17"/>
       <c r="D526" s="18"/>
       <c r="E526" s="22">
-        <f t="shared" ref="E526:E589" si="8">SUM(F526:P527)+ SUM(R526+V526)</f>
+        <f t="shared" ref="E526:E589" si="8">SUM(F526:V526) -Q526</f>
         <v>0</v>
       </c>
       <c r="F526" s="19"/>
@@ -16860,7 +16860,7 @@
       <c r="C590" s="17"/>
       <c r="D590" s="18"/>
       <c r="E590" s="22">
-        <f t="shared" ref="E590:E653" si="9">SUM(F590:P591)+ SUM(R590+V590)</f>
+        <f t="shared" ref="E590:E653" si="9">SUM(F590:V590) -Q590</f>
         <v>0</v>
       </c>
       <c r="F590" s="19"/>
@@ -18588,7 +18588,7 @@
       <c r="C654" s="17"/>
       <c r="D654" s="18"/>
       <c r="E654" s="22">
-        <f t="shared" ref="E654:E701" si="10">SUM(F654:P655)+ SUM(R654+V654)</f>
+        <f t="shared" ref="E654:E701" si="10">SUM(F654:V654) -Q654</f>
         <v>0</v>
       </c>
       <c r="F654" s="19"/>
@@ -19880,18 +19880,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A7:V7"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="A5:V5"/>
     <mergeCell ref="A6:V6"/>
@@ -19908,6 +19896,18 @@
     <mergeCell ref="P9:Q9"/>
     <mergeCell ref="U9:U10"/>
     <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A7:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="49" orientation="landscape" r:id="rId1"/>

--- a/web/EXCEL_TEMPLATE/KHNV/KHNV_01C_2026.xlsx
+++ b/web/EXCEL_TEMPLATE/KHNV/KHNV_01C_2026.xlsx
@@ -534,8 +534,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -543,20 +552,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -866,68 +866,68 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="33"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
     </row>
     <row r="2" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
+      <c r="A2" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
     </row>
     <row r="3" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
     </row>
     <row r="4" spans="1:22" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
@@ -946,78 +946,78 @@
       <c r="Q4" s="20"/>
     </row>
     <row r="5" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
     </row>
     <row r="6" spans="1:22" s="26" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="32"/>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="32"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="32"/>
-      <c r="T7" s="32"/>
-      <c r="U7" s="32"/>
-      <c r="V7" s="32"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34"/>
     </row>
     <row r="8" spans="1:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
@@ -1061,53 +1061,53 @@
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="H9" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="I9" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="31" t="s">
+      <c r="J9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K9" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L9" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="31" t="s">
+      <c r="M9" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="31" t="s">
+      <c r="N9" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="P9" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31" t="s">
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="31" t="s">
+      <c r="S9" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="T9" s="31" t="s">
+      <c r="T9" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="U9" s="28" t="s">
+      <c r="U9" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="V9" s="28" t="s">
+      <c r="V9" s="31" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1117,27 +1117,27 @@
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
       <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
       <c r="P10" s="24" t="s">
         <v>40</v>
       </c>
       <c r="Q10" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
@@ -19880,6 +19880,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A7:V7"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="A5:V5"/>
     <mergeCell ref="A6:V6"/>
@@ -19896,20 +19908,8 @@
     <mergeCell ref="P9:Q9"/>
     <mergeCell ref="U9:U10"/>
     <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A3:V3"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="C8:C10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A7:V7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="49" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="47" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>